--- a/Mocks/Key_DB.xlsx
+++ b/Mocks/Key_DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\OneDrive\Desktop\Projects\Ideas\CLAUD\RecallTxtChecker\Mocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FEB22FC-E6B0-4418-85E1-AFC067DDF8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A39B6D2-8BE0-4D78-8CFB-8CC06960D7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B279F4D-AF20-45DA-A861-4760F6419F18}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="88">
   <si>
     <t>End User</t>
   </si>
@@ -176,9 +176,6 @@
     <t>68399889AA</t>
   </si>
   <si>
-    <t>Ford Dtown</t>
-  </si>
-  <si>
     <t>1FMJK2AT3NEA53302</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
     <t>F350</t>
   </si>
   <si>
-    <t>MTB</t>
-  </si>
-  <si>
     <t>4/27/26</t>
   </si>
   <si>
@@ -246,6 +240,69 @@
   </si>
   <si>
     <t>Total Parts Cost</t>
+  </si>
+  <si>
+    <t>Chevrolet</t>
+  </si>
+  <si>
+    <t>MTB Landscapig</t>
+  </si>
+  <si>
+    <t>8990H-0E370</t>
+  </si>
+  <si>
+    <t>69515-16110</t>
+  </si>
+  <si>
+    <t>5TDKDRBHXPS010062</t>
+  </si>
+  <si>
+    <t>Highlander</t>
+  </si>
+  <si>
+    <t>72147-TVA-A12</t>
+  </si>
+  <si>
+    <t>35118-T2A-A50</t>
+  </si>
+  <si>
+    <t>1HGCV1F33NA117418</t>
+  </si>
+  <si>
+    <t>1GB3YSE70PF240782</t>
+  </si>
+  <si>
+    <t>KL79MUSL1PB142623</t>
+  </si>
+  <si>
+    <t>5NPEC4AC9DH629746</t>
+  </si>
+  <si>
+    <t>95440-3Q000</t>
+  </si>
+  <si>
+    <t>81996-3S020</t>
+  </si>
+  <si>
+    <t>Hyundai</t>
+  </si>
+  <si>
+    <t>Sonata</t>
+  </si>
+  <si>
+    <t>Trailblazer</t>
+  </si>
+  <si>
+    <t>Slverado</t>
+  </si>
+  <si>
+    <t>Honda</t>
+  </si>
+  <si>
+    <t>Accord</t>
+  </si>
+  <si>
+    <t>4/15/2026</t>
   </si>
 </sst>
 </file>
@@ -317,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -340,20 +397,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -670,23 +723,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E28BE2CD-44E5-49C0-B421-2ADAB672C8D3}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="15.7109375" customWidth="1"/>
+    <col min="1" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="10" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="19" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>1</v>
@@ -719,7 +773,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>11</v>
@@ -737,147 +791,147 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>23</v>
+      <c r="C2" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="D2" s="1">
         <v>314380</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>59</v>
+      <c r="E2" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="F2" s="1">
         <v>2020</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="1">
         <v>84209236</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="1">
         <v>114.02</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="1">
         <v>13523912</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="1">
         <v>37.090000000000003</v>
       </c>
       <c r="N2" s="3">
-        <f>SUM(K2,M2)</f>
+        <f t="shared" ref="N2:N15" si="0">SUM(K2,M2)</f>
         <v>151.11000000000001</v>
       </c>
       <c r="O2" s="3">
         <v>60</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="3">
         <f>SUM(N2:O2)</f>
         <v>211.11</v>
       </c>
-      <c r="Q2" s="11">
-        <f>ROUND(N2*0.3,0)</f>
+      <c r="Q2" s="3">
+        <f t="shared" ref="Q2:Q15" si="1">ROUND(N2*0.3,0)</f>
         <v>45</v>
       </c>
-      <c r="R2" s="11">
-        <f t="shared" ref="R2:R4" si="0">P2-Q2</f>
+      <c r="R2" s="3">
+        <f t="shared" ref="R2:R4" si="2">P2-Q2</f>
         <v>166.11</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="8">
         <v>314326</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2021</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="10">
-        <v>2021</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="1">
         <v>13544052</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="1">
         <v>102.95</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="1">
         <v>22984994</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="1">
         <v>52.18</v>
       </c>
       <c r="N3" s="3">
-        <f>SUM(K3,M3)</f>
+        <f t="shared" si="0"/>
         <v>155.13</v>
       </c>
       <c r="O3" s="3">
         <v>60</v>
       </c>
-      <c r="P3" s="11">
-        <f t="shared" ref="P3:P15" si="1">SUM(N3:O3)</f>
+      <c r="P3" s="3">
+        <f t="shared" ref="P3:P15" si="3">SUM(N3:O3)</f>
         <v>215.13</v>
       </c>
-      <c r="Q3" s="11">
-        <f>ROUND(N3*0.3,0)</f>
+      <c r="Q3" s="3">
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="R3" s="11">
-        <f t="shared" si="0"/>
+      <c r="R3" s="3">
+        <f t="shared" si="2"/>
         <v>168.13</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="1">
         <v>314379</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>64</v>
+      <c r="E4" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="F4" s="1">
         <v>2023</v>
@@ -886,61 +940,61 @@
         <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="1">
         <v>5929503</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="1">
         <v>148.5</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="1">
         <v>5939649</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="1">
         <v>36.29</v>
       </c>
       <c r="N4" s="3">
-        <f>SUM(K4,M4)</f>
+        <f t="shared" si="0"/>
         <v>184.79</v>
       </c>
       <c r="O4" s="3">
         <v>60</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="3">
+        <f t="shared" si="3"/>
+        <v>244.79</v>
+      </c>
+      <c r="Q4" s="3">
         <f t="shared" si="1"/>
-        <v>244.79</v>
-      </c>
-      <c r="Q4" s="11">
-        <f>ROUND(N4*0.3,0)</f>
         <v>55</v>
       </c>
-      <c r="R4" s="11">
-        <f t="shared" si="0"/>
+      <c r="R4" s="3">
+        <f t="shared" si="2"/>
         <v>189.79</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="8">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1">
         <v>314397</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>55</v>
+      <c r="E5" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="F5" s="1">
         <v>2026</v>
@@ -949,106 +1003,106 @@
         <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" s="8">
+        <v>55</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="1">
         <v>5945864</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="1">
         <v>128.69999999999999</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="N5" s="3">
-        <f>SUM(K5,M5)</f>
+        <f t="shared" si="0"/>
         <v>128.69999999999999</v>
       </c>
       <c r="O5" s="3">
         <v>60</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="3">
+        <f t="shared" si="3"/>
+        <v>188.7</v>
+      </c>
+      <c r="Q5" s="3">
         <f t="shared" si="1"/>
-        <v>188.7</v>
-      </c>
-      <c r="Q5" s="11">
-        <f>ROUND(N5*0.3,0)</f>
         <v>39</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="3">
         <f>P5-Q5</f>
         <v>149.69999999999999</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="S5" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46027</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="1">
         <v>314398</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2017</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="8">
-        <v>2017</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="1">
         <v>5926054</v>
       </c>
       <c r="K6" s="3">
         <v>165</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="1">
         <v>4223891</v>
       </c>
       <c r="M6" s="3">
         <v>30.31</v>
       </c>
       <c r="N6" s="3">
-        <f>SUM(K6,M6)</f>
+        <f t="shared" si="0"/>
         <v>195.31</v>
       </c>
       <c r="O6" s="3">
         <v>60</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6" s="3">
+        <f t="shared" si="3"/>
+        <v>255.31</v>
+      </c>
+      <c r="Q6" s="3">
         <f t="shared" si="1"/>
-        <v>255.31</v>
-      </c>
-      <c r="Q6" s="11">
-        <f>ROUND(N6*0.3,0)</f>
         <v>59</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="3">
         <f>P6-Q6</f>
         <v>196.31</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="S6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1093,22 +1147,22 @@
         <v>36.29</v>
       </c>
       <c r="N7" s="3">
-        <f>SUM(K7,M7)</f>
+        <f t="shared" si="0"/>
         <v>193.54</v>
       </c>
       <c r="O7" s="3">
         <v>60</v>
       </c>
-      <c r="P7" s="11">
+      <c r="P7" s="3">
+        <f t="shared" si="3"/>
+        <v>253.54</v>
+      </c>
+      <c r="Q7" s="3">
         <f t="shared" si="1"/>
-        <v>253.54</v>
-      </c>
-      <c r="Q7" s="11">
-        <f>ROUND(N7*0.3,0)</f>
         <v>58</v>
       </c>
-      <c r="R7" s="11">
-        <f t="shared" ref="R7:R15" si="2">P7-Q7</f>
+      <c r="R7" s="3">
+        <f t="shared" ref="R7:R15" si="4">P7-Q7</f>
         <v>195.54</v>
       </c>
       <c r="S7" s="1" t="s">
@@ -1123,7 +1177,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D8" s="1">
         <v>314503</v>
@@ -1156,22 +1210,22 @@
         <v>36.29</v>
       </c>
       <c r="N8" s="3">
-        <f>SUM(K8,M8)</f>
+        <f t="shared" si="0"/>
         <v>193.54</v>
       </c>
       <c r="O8" s="3">
         <v>60</v>
       </c>
-      <c r="P8" s="11">
+      <c r="P8" s="3">
+        <f t="shared" si="3"/>
+        <v>253.54</v>
+      </c>
+      <c r="Q8" s="3">
         <f t="shared" si="1"/>
-        <v>253.54</v>
-      </c>
-      <c r="Q8" s="11">
-        <f>ROUND(N8*0.3,0)</f>
         <v>58</v>
       </c>
-      <c r="R8" s="11">
-        <f t="shared" si="2"/>
+      <c r="R8" s="3">
+        <f t="shared" si="4"/>
         <v>195.54</v>
       </c>
       <c r="S8" s="1" t="s">
@@ -1186,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1">
         <v>314502</v>
@@ -1219,22 +1273,22 @@
         <v>66.31</v>
       </c>
       <c r="N9" s="3">
-        <f>SUM(K9,M9)</f>
+        <f t="shared" si="0"/>
         <v>172.76999999999998</v>
       </c>
       <c r="O9" s="3">
         <v>60</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="3">
+        <f t="shared" si="3"/>
+        <v>232.76999999999998</v>
+      </c>
+      <c r="Q9" s="3">
         <f t="shared" si="1"/>
-        <v>232.76999999999998</v>
-      </c>
-      <c r="Q9" s="11">
-        <f>ROUND(N9*0.3,0)</f>
         <v>52</v>
       </c>
-      <c r="R9" s="11">
-        <f t="shared" si="2"/>
+      <c r="R9" s="3">
+        <f t="shared" si="4"/>
         <v>180.76999999999998</v>
       </c>
       <c r="S9" s="1" t="s">
@@ -1282,22 +1336,22 @@
         <v>6.04</v>
       </c>
       <c r="N10" s="3">
-        <f>SUM(K10,M10)</f>
+        <f t="shared" si="0"/>
         <v>6.04</v>
       </c>
       <c r="O10" s="3">
         <v>60</v>
       </c>
-      <c r="P10" s="11">
+      <c r="P10" s="3">
+        <f t="shared" si="3"/>
+        <v>66.040000000000006</v>
+      </c>
+      <c r="Q10" s="3">
         <f t="shared" si="1"/>
-        <v>66.040000000000006</v>
-      </c>
-      <c r="Q10" s="11">
-        <f>ROUND(N10*0.3,0)</f>
         <v>2</v>
       </c>
-      <c r="R10" s="11">
-        <f t="shared" si="2"/>
+      <c r="R10" s="3">
+        <f t="shared" si="4"/>
         <v>64.040000000000006</v>
       </c>
       <c r="S10" s="1" t="s">
@@ -1345,22 +1399,22 @@
         <v>43.12</v>
       </c>
       <c r="N11" s="3">
-        <f>SUM(K11,M11)</f>
+        <f t="shared" si="0"/>
         <v>182.82</v>
       </c>
       <c r="O11" s="3">
         <v>60</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="3">
+        <f t="shared" si="3"/>
+        <v>242.82</v>
+      </c>
+      <c r="Q11" s="3">
         <f t="shared" si="1"/>
-        <v>242.82</v>
-      </c>
-      <c r="Q11" s="11">
-        <f>ROUND(N11*0.3,0)</f>
         <v>55</v>
       </c>
-      <c r="R11" s="11">
-        <f t="shared" si="2"/>
+      <c r="R11" s="3">
+        <f t="shared" si="4"/>
         <v>187.82</v>
       </c>
       <c r="S11" s="1" t="s">
@@ -1375,7 +1429,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D12" s="1">
         <v>314571</v>
@@ -1408,22 +1462,22 @@
         <v>29.81</v>
       </c>
       <c r="N12" s="3">
-        <f>SUM(K12,M12)</f>
+        <f t="shared" si="0"/>
         <v>93.83</v>
       </c>
       <c r="O12" s="3">
         <v>60</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="3">
+        <f t="shared" si="3"/>
+        <v>153.82999999999998</v>
+      </c>
+      <c r="Q12" s="3">
         <f t="shared" si="1"/>
-        <v>153.82999999999998</v>
-      </c>
-      <c r="Q12" s="11">
-        <f>ROUND(N12*0.3,0)</f>
         <v>28</v>
       </c>
-      <c r="R12" s="11">
-        <f t="shared" si="2"/>
+      <c r="R12" s="3">
+        <f t="shared" si="4"/>
         <v>125.82999999999998</v>
       </c>
       <c r="S12" s="1" t="s">
@@ -1438,7 +1492,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1">
         <v>314572</v>
@@ -1471,22 +1525,22 @@
         <v>36.29</v>
       </c>
       <c r="N13" s="3">
-        <f>SUM(K13,M13)</f>
+        <f t="shared" si="0"/>
         <v>193.54</v>
       </c>
       <c r="O13" s="3">
         <v>60</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="3">
+        <f t="shared" si="3"/>
+        <v>253.54</v>
+      </c>
+      <c r="Q13" s="3">
         <f t="shared" si="1"/>
-        <v>253.54</v>
-      </c>
-      <c r="Q13" s="11">
-        <f>ROUND(N13*0.3,0)</f>
         <v>58</v>
       </c>
-      <c r="R13" s="11">
-        <f t="shared" si="2"/>
+      <c r="R13" s="3">
+        <f t="shared" si="4"/>
         <v>195.54</v>
       </c>
       <c r="S13" s="1" t="s">
@@ -1501,13 +1555,13 @@
         <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
         <v>314573</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1">
         <v>2022</v>
@@ -1516,7 +1570,7 @@
         <v>19</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>21</v>
@@ -1534,22 +1588,22 @@
         <v>36.29</v>
       </c>
       <c r="N14" s="3">
-        <f>SUM(K14,M14)</f>
+        <f t="shared" si="0"/>
         <v>197.17</v>
       </c>
       <c r="O14" s="3">
         <v>60</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="3">
+        <f t="shared" si="3"/>
+        <v>257.16999999999996</v>
+      </c>
+      <c r="Q14" s="3">
         <f t="shared" si="1"/>
-        <v>257.16999999999996</v>
-      </c>
-      <c r="Q14" s="11">
-        <f>ROUND(N14*0.3,0)</f>
         <v>59</v>
       </c>
-      <c r="R14" s="11">
-        <f t="shared" si="2"/>
+      <c r="R14" s="3">
+        <f t="shared" si="4"/>
         <v>198.16999999999996</v>
       </c>
       <c r="S14" s="1" t="s">
@@ -1561,16 +1615,16 @@
         <v>46331</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="1">
         <v>2023</v>
@@ -1579,10 +1633,10 @@
         <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="J15" s="1">
         <v>5923694</v>
@@ -1597,25 +1651,340 @@
         <v>33</v>
       </c>
       <c r="N15" s="3">
-        <f>SUM(K15,M15)</f>
+        <f t="shared" si="0"/>
         <v>134.19999999999999</v>
       </c>
       <c r="O15" s="3">
         <v>60</v>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="3">
+        <f t="shared" si="3"/>
+        <v>194.2</v>
+      </c>
+      <c r="Q15" s="3">
         <f t="shared" si="1"/>
-        <v>194.2</v>
-      </c>
-      <c r="Q15" s="11">
-        <f>ROUND(N15*0.3,0)</f>
         <v>40</v>
       </c>
-      <c r="R15" s="11">
-        <f t="shared" si="2"/>
+      <c r="R15" s="3">
+        <f t="shared" si="4"/>
         <v>154.19999999999999</v>
       </c>
       <c r="S15" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="3">
+        <v>135.62</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="3">
+        <v>24.19</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" ref="N17:N21" si="5">SUM(K17,M17)</f>
+        <v>159.81</v>
+      </c>
+      <c r="O17" s="3">
+        <v>60</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" ref="P17:P21" si="6">SUM(N17:O17)</f>
+        <v>219.81</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" ref="Q17:Q21" si="7">ROUND(N17*0.3,0)</f>
+        <v>48</v>
+      </c>
+      <c r="R17" s="3">
+        <f t="shared" ref="R17:R21" si="8">P17-Q17</f>
+        <v>171.81</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="10">
+        <v>314276</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="3">
+        <v>84.88</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" s="3">
+        <v>28.63</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="5"/>
+        <v>113.50999999999999</v>
+      </c>
+      <c r="O18" s="3">
+        <v>60</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="6"/>
+        <v>173.51</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="8"/>
+        <v>139.51</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="10">
+        <v>314277</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="10">
+        <v>2023</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="10">
+        <v>13577765</v>
+      </c>
+      <c r="K19" s="3">
+        <v>64.17</v>
+      </c>
+      <c r="L19" s="10">
+        <v>13523912</v>
+      </c>
+      <c r="M19" s="3">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="5"/>
+        <v>101.26</v>
+      </c>
+      <c r="O19" s="3">
+        <v>60</v>
+      </c>
+      <c r="P19" s="3">
+        <f t="shared" si="6"/>
+        <v>161.26</v>
+      </c>
+      <c r="Q19" s="3">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="R19" s="3">
+        <f t="shared" si="8"/>
+        <v>131.26</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="10">
+        <v>314275</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="10">
+        <v>2023</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="10">
+        <v>13547830</v>
+      </c>
+      <c r="K20" s="3">
+        <v>94.3</v>
+      </c>
+      <c r="L20" s="10">
+        <v>13523213</v>
+      </c>
+      <c r="M20" s="3">
+        <v>52.18</v>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="5"/>
+        <v>146.47999999999999</v>
+      </c>
+      <c r="O20" s="3">
+        <v>60</v>
+      </c>
+      <c r="P20" s="3">
+        <f t="shared" si="6"/>
+        <v>206.48</v>
+      </c>
+      <c r="Q20" s="3">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="R20" s="3">
+        <f t="shared" si="8"/>
+        <v>162.47999999999999</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="10">
+        <v>314121</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="10">
+        <v>2013</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="3">
+        <v>352.32</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="3">
+        <v>19.82</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="5"/>
+        <v>372.14</v>
+      </c>
+      <c r="O21" s="3">
+        <v>60</v>
+      </c>
+      <c r="P21" s="3">
+        <f t="shared" si="6"/>
+        <v>432.14</v>
+      </c>
+      <c r="Q21" s="3">
+        <f t="shared" si="7"/>
+        <v>112</v>
+      </c>
+      <c r="R21" s="3">
+        <f t="shared" si="8"/>
+        <v>320.14</v>
+      </c>
+      <c r="S21" s="6" t="s">
         <v>27</v>
       </c>
     </row>
